--- a/00001/Lista_Octava_Salvatierra.xlsx
+++ b/00001/Lista_Octava_Salvatierra.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jorge\OneDrive\Documentos\Liga\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\lavalle-liga\00001\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{33504A25-2BAB-4BFC-AC62-7CD253683E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E68ADF74-94BF-411C-BDD3-B8A7DA2FBED2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{23FF5CE4-7B3D-4597-BAAE-33B74D8AE677}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{23FF5CE4-7B3D-4597-BAAE-33B74D8AE677}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -19,17 +19,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
@@ -44,9 +33,6 @@
     <t>N°</t>
   </si>
   <si>
-    <t>APELLIDO - NOMBRE</t>
-  </si>
-  <si>
     <t>DNI</t>
   </si>
   <si>
@@ -119,17 +105,20 @@
     <t>N° Carnet</t>
   </si>
   <si>
-    <t>Categoría</t>
-  </si>
-  <si>
     <t>Club</t>
+  </si>
+  <si>
+    <t>APELLIDO y NOMBRE</t>
+  </si>
+  <si>
+    <t>Cat</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -533,52 +522,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D659123B-88ED-4304-AE25-715C0A45D254}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="32.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="32.5" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>4</v>
       </c>
       <c r="C2" s="7">
         <v>53667285</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" s="6">
         <v>1118</v>
@@ -590,18 +579,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" s="7">
         <v>53664440</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E3" s="6">
         <v>1119</v>
@@ -613,18 +602,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" s="7">
         <v>53658619</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4" s="6">
         <v>1120</v>
@@ -636,18 +625,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="7">
         <v>54538480</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E5" s="6">
         <v>1121</v>
@@ -659,18 +648,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="7">
         <v>54922918</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" s="6">
         <v>1122</v>
@@ -682,18 +671,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="7">
         <v>55384393</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7" s="6">
         <v>1123</v>
@@ -705,18 +694,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="7">
         <v>55541593</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8" s="6">
         <v>1124</v>
@@ -728,18 +717,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" s="7">
         <v>53944814</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E9" s="6">
         <v>1125</v>
@@ -751,18 +740,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" s="7">
         <v>54167723</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E10" s="6">
         <v>1126</v>
@@ -774,18 +763,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" s="3">
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" s="7">
         <v>53938265</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E11" s="6">
         <v>1110</v>
@@ -797,18 +786,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12" s="3">
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="7">
         <v>55136239</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E12" s="6">
         <v>1111</v>
@@ -820,18 +809,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13" s="3">
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" s="7">
         <v>53658697</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E13" s="6">
         <v>1112</v>
@@ -843,18 +832,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14" s="3">
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" s="7">
         <v>53945594</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E14" s="6">
         <v>1113</v>
@@ -866,18 +855,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15" s="3">
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" s="7">
         <v>53491728</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E15" s="6">
         <v>1114</v>
@@ -889,18 +878,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" s="3">
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" s="7">
         <v>54167010</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E16" s="6">
         <v>1115</v>
@@ -912,18 +901,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" s="3">
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17" s="7">
         <v>55547469</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E17" s="6">
         <v>1116</v>
@@ -935,18 +924,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18" s="3">
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C18" s="7">
         <v>56080040</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E18" s="6">
         <v>1117</v>

--- a/00001/Lista_Octava_Salvatierra.xlsx
+++ b/00001/Lista_Octava_Salvatierra.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\lavalle-liga\00001\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E68ADF74-94BF-411C-BDD3-B8A7DA2FBED2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB6882A-6CAD-457F-9EDD-1D0859EFE4A6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{23FF5CE4-7B3D-4597-BAAE-33B74D8AE677}"/>
   </bookViews>
@@ -166,25 +166,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -534,16 +530,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -557,393 +553,393 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="5">
         <v>53667285</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="6">
-        <v>1118</v>
-      </c>
-      <c r="F2" s="6">
-        <v>7</v>
-      </c>
-      <c r="G2" s="6">
+      <c r="E2">
+        <v>2018</v>
+      </c>
+      <c r="F2">
+        <v>7</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="5">
         <v>53664440</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="6">
-        <v>1119</v>
-      </c>
-      <c r="F3" s="6">
-        <v>7</v>
-      </c>
-      <c r="G3" s="6">
+      <c r="E3">
+        <v>2019</v>
+      </c>
+      <c r="F3">
+        <v>7</v>
+      </c>
+      <c r="G3">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="5">
         <v>53658619</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="6">
-        <v>1120</v>
-      </c>
-      <c r="F4" s="6">
-        <v>7</v>
-      </c>
-      <c r="G4" s="6">
+      <c r="E4">
+        <v>2020</v>
+      </c>
+      <c r="F4">
+        <v>7</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="5">
         <v>54538480</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="6">
-        <v>1121</v>
-      </c>
-      <c r="F5" s="6">
-        <v>7</v>
-      </c>
-      <c r="G5" s="6">
+      <c r="E5">
+        <v>2021</v>
+      </c>
+      <c r="F5">
+        <v>7</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="5">
         <v>54922918</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="6">
-        <v>1122</v>
-      </c>
-      <c r="F6" s="6">
-        <v>7</v>
-      </c>
-      <c r="G6" s="6">
+      <c r="E6">
+        <v>2022</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="3">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="7">
+      <c r="B7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="5">
         <v>55384393</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="6">
-        <v>1123</v>
-      </c>
-      <c r="F7" s="6">
-        <v>7</v>
-      </c>
-      <c r="G7" s="6">
+      <c r="E7">
+        <v>2023</v>
+      </c>
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="3">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="5">
         <v>55541593</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="6">
-        <v>1124</v>
-      </c>
-      <c r="F8" s="6">
-        <v>7</v>
-      </c>
-      <c r="G8" s="6">
+      <c r="E8">
+        <v>2024</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+      <c r="G8">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="3">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="5">
         <v>53944814</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="6">
-        <v>1125</v>
-      </c>
-      <c r="F9" s="6">
-        <v>7</v>
-      </c>
-      <c r="G9" s="6">
+      <c r="E9">
+        <v>2025</v>
+      </c>
+      <c r="F9">
+        <v>7</v>
+      </c>
+      <c r="G9">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="3">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="5">
         <v>54167723</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="6">
-        <v>1126</v>
-      </c>
-      <c r="F10" s="6">
-        <v>7</v>
-      </c>
-      <c r="G10" s="6">
+      <c r="E10">
+        <v>2026</v>
+      </c>
+      <c r="F10">
+        <v>7</v>
+      </c>
+      <c r="G10">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="3">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="5">
         <v>53938265</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="6">
-        <v>1110</v>
-      </c>
-      <c r="F11" s="6">
-        <v>7</v>
-      </c>
-      <c r="G11" s="6">
+      <c r="E11">
+        <v>2027</v>
+      </c>
+      <c r="F11">
+        <v>7</v>
+      </c>
+      <c r="G11">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="3">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="5">
         <v>55136239</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="6">
-        <v>1111</v>
-      </c>
-      <c r="F12" s="6">
-        <v>7</v>
-      </c>
-      <c r="G12" s="6">
+      <c r="E12">
+        <v>2028</v>
+      </c>
+      <c r="F12">
+        <v>7</v>
+      </c>
+      <c r="G12">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="3">
+      <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="5">
         <v>53658697</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="6">
-        <v>1112</v>
-      </c>
-      <c r="F13" s="6">
-        <v>7</v>
-      </c>
-      <c r="G13" s="6">
+      <c r="E13">
+        <v>2029</v>
+      </c>
+      <c r="F13">
+        <v>7</v>
+      </c>
+      <c r="G13">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="3">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="5">
         <v>53945594</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="6">
-        <v>1113</v>
-      </c>
-      <c r="F14" s="6">
-        <v>7</v>
-      </c>
-      <c r="G14" s="6">
+      <c r="E14">
+        <v>2030</v>
+      </c>
+      <c r="F14">
+        <v>7</v>
+      </c>
+      <c r="G14">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="3">
+      <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="5">
         <v>53491728</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="6">
-        <v>1114</v>
-      </c>
-      <c r="F15" s="6">
-        <v>7</v>
-      </c>
-      <c r="G15" s="6">
+      <c r="E15">
+        <v>2031</v>
+      </c>
+      <c r="F15">
+        <v>7</v>
+      </c>
+      <c r="G15">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="3">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="5">
         <v>54167010</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="6">
-        <v>1115</v>
-      </c>
-      <c r="F16" s="6">
-        <v>7</v>
-      </c>
-      <c r="G16" s="6">
+      <c r="E16">
+        <v>2032</v>
+      </c>
+      <c r="F16">
+        <v>7</v>
+      </c>
+      <c r="G16">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="3">
+      <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="5">
         <v>55547469</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="6">
-        <v>1116</v>
-      </c>
-      <c r="F17" s="6">
-        <v>7</v>
-      </c>
-      <c r="G17" s="6">
+      <c r="E17">
+        <v>2033</v>
+      </c>
+      <c r="F17">
+        <v>7</v>
+      </c>
+      <c r="G17">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="3">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="5">
         <v>56080040</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="6">
-        <v>1117</v>
-      </c>
-      <c r="F18" s="6">
-        <v>7</v>
-      </c>
-      <c r="G18" s="6">
+      <c r="E18">
+        <v>2034</v>
+      </c>
+      <c r="F18">
+        <v>7</v>
+      </c>
+      <c r="G18">
         <v>1</v>
       </c>
     </row>
